--- a/dist/collections.xlsx
+++ b/dist/collections.xlsx
@@ -4,14 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13500" activeTab="4"/>
+    <workbookView windowHeight="17655" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="players" sheetId="1" r:id="rId1"/>
     <sheet name="player_level_best" sheetId="2" r:id="rId2"/>
     <sheet name="player_difficulty_summary" sheetId="3" r:id="rId3"/>
-    <sheet name="region_difficulty_stats" sheetId="4" r:id="rId4"/>
-    <sheet name="level_stats" sheetId="5" r:id="rId5"/>
+    <sheet name="level_stats" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="61">
   <si>
     <t>字段名</t>
   </si>
@@ -90,24 +89,6 @@
     <t>https://example.com/avatar.png</t>
   </si>
   <si>
-    <t>regionCode</t>
-  </si>
-  <si>
-    <t>地区编码，建议使用稳定值，例如 guangdong，方便统计和查询。</t>
-  </si>
-  <si>
-    <t>guangdong</t>
-  </si>
-  <si>
-    <t>regionName</t>
-  </si>
-  <si>
-    <t>地区中文名称，用于前端直接展示。</t>
-  </si>
-  <si>
-    <t>广东</t>
-  </si>
-  <si>
     <t>createdAt</t>
   </si>
   <si>
@@ -189,12 +170,6 @@
     <t>冗余保存头像，方便难度总榜直接展示。</t>
   </si>
   <si>
-    <t>玩家所属地区编码。</t>
-  </si>
-  <si>
-    <t>玩家所属地区名称。</t>
-  </si>
-  <si>
     <t>highestLevel</t>
   </si>
   <si>
@@ -204,58 +179,25 @@
     <t>12</t>
   </si>
   <si>
-    <t>文档主键，建议格式为 statDate#difficulty#regionCode。</t>
-  </si>
-  <si>
-    <t>2026-04-14#easy#guangdong</t>
-  </si>
-  <si>
-    <t>statDate</t>
-  </si>
-  <si>
-    <t>统计日期，建议使用 YYYY-MM-DD 格式。</t>
-  </si>
-  <si>
-    <t>2026-04-14</t>
+    <t>文档主键，建议格式为 difficulty#levelNo。</t>
+  </si>
+  <si>
+    <t>easy#1</t>
   </si>
   <si>
     <t>难度编码。</t>
   </si>
   <si>
-    <t>地区编码，用于稳定查询和排序。</t>
-  </si>
-  <si>
-    <t>地区名称，用于前端展示，例如广东。</t>
-  </si>
-  <si>
     <t>clearCount</t>
   </si>
   <si>
-    <t>该日期、该地区、该难度下的总通关次数。</t>
-  </si>
-  <si>
-    <t>3288</t>
+    <t>该关卡累计通关次数。</t>
+  </si>
+  <si>
+    <t>15382</t>
   </si>
   <si>
     <t>uniquePlayerCount</t>
-  </si>
-  <si>
-    <t>该日期、该地区、该难度下的去重通关人数。</t>
-  </si>
-  <si>
-    <t>905</t>
-  </si>
-  <si>
-    <t>文档主键，建议格式为 difficulty#levelNo。</t>
-  </si>
-  <si>
-    <t>easy#1</t>
-  </si>
-  <si>
-    <t>该关卡累计通关次数。</t>
-  </si>
-  <si>
-    <t>15382</t>
   </si>
   <si>
     <t>该关卡累计通关人数。</t>
@@ -1254,8 +1196,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="4"/>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -1332,7 +1274,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" ht="28.8" spans="1:5">
+    <row r="5" ht="27" spans="1:5">
       <c r="A5" s="2" t="s">
         <v>15</v>
       </c>
@@ -1354,33 +1296,33 @@
         <v>19</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1388,50 +1330,16 @@
         <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1444,7 +1352,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -1481,10 +1389,10 @@
         <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1498,7 +1406,7 @@
         <v>7</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>9</v>
@@ -1506,7 +1414,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>6</v>
@@ -1515,27 +1423,27 @@
         <v>7</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1549,13 +1457,13 @@
         <v>7</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" ht="28.8" spans="1:5">
+    <row r="7" ht="27" spans="1:5">
       <c r="A7" s="2" t="s">
         <v>15</v>
       </c>
@@ -1566,24 +1474,24 @@
         <v>16</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="8" ht="28.8" spans="1:5">
+    <row r="8" ht="27" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="E8" s="3">
         <v>180</v>
@@ -1598,8 +1506,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="4"/>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -1636,10 +1544,10 @@
         <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1653,7 +1561,7 @@
         <v>7</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>9</v>
@@ -1661,7 +1569,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>6</v>
@@ -1670,10 +1578,10 @@
         <v>7</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1687,13 +1595,13 @@
         <v>7</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" ht="28.8" spans="1:5">
+    <row r="6" ht="27" spans="1:5">
       <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
@@ -1704,7 +1612,7 @@
         <v>16</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>18</v>
@@ -1712,53 +1620,19 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1771,7 +1645,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -1808,15 +1682,15 @@
         <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>6</v>
@@ -1825,247 +1699,92 @@
         <v>7</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>67</v>
+        <v>58</v>
+      </c>
+      <c r="E7" s="3">
+        <v>150</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="4"/>
-  <cols>
-    <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="60" customWidth="1"/>
-    <col min="5" max="5" width="28" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E7" s="3">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="E8" s="3">
         <v>238</v>

--- a/dist/collections.xlsx
+++ b/dist/collections.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="2"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="players" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="58">
   <si>
     <t>字段名</t>
   </si>
@@ -105,15 +105,6 @@
   </si>
   <si>
     <t>最后一次登录时间。</t>
-  </si>
-  <si>
-    <t>lastActiveAt</t>
-  </si>
-  <si>
-    <t>最后一次活跃时间，用于判断玩家最近是否在线。</t>
-  </si>
-  <si>
-    <t>2026-04-14T10:30:00.000Z</t>
   </si>
   <si>
     <t>文档主键，建议格式为 difficulty#levelNo#userId。</t>
@@ -1196,8 +1187,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="4"/>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -1323,23 +1314,6 @@
       </c>
       <c r="E7" s="2" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1389,10 +1363,10 @@
         <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1406,7 +1380,7 @@
         <v>7</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>9</v>
@@ -1414,7 +1388,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>6</v>
@@ -1423,27 +1397,27 @@
         <v>7</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1457,7 +1431,7 @@
         <v>7</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>14</v>
@@ -1474,7 +1448,7 @@
         <v>16</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>18</v>
@@ -1482,16 +1456,16 @@
     </row>
     <row r="8" ht="27" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E8" s="3">
         <v>180</v>
@@ -1544,10 +1518,10 @@
         <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1561,7 +1535,7 @@
         <v>7</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>9</v>
@@ -1569,7 +1543,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>6</v>
@@ -1578,10 +1552,10 @@
         <v>7</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1595,7 +1569,7 @@
         <v>7</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>14</v>
@@ -1612,7 +1586,7 @@
         <v>16</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>18</v>
@@ -1620,19 +1594,19 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1682,15 +1656,15 @@
         <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>6</v>
@@ -1699,75 +1673,75 @@
         <v>7</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E7" s="3">
         <v>150</v>
@@ -1775,16 +1749,16 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E8" s="3">
         <v>238</v>

--- a/dist/collections.xlsx
+++ b/dist/collections.xlsx
@@ -4,13 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowHeight="17655" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="players" sheetId="1" r:id="rId1"/>
     <sheet name="player_level_best" sheetId="2" r:id="rId2"/>
     <sheet name="player_difficulty_summary" sheetId="3" r:id="rId3"/>
-    <sheet name="level_stats" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="46">
   <si>
     <t>字段名</t>
   </si>
@@ -168,42 +167,6 @@
   </si>
   <si>
     <t>12</t>
-  </si>
-  <si>
-    <t>文档主键，建议格式为 difficulty#levelNo。</t>
-  </si>
-  <si>
-    <t>easy#1</t>
-  </si>
-  <si>
-    <t>难度编码。</t>
-  </si>
-  <si>
-    <t>clearCount</t>
-  </si>
-  <si>
-    <t>该关卡累计通关次数。</t>
-  </si>
-  <si>
-    <t>15382</t>
-  </si>
-  <si>
-    <t>uniquePlayerCount</t>
-  </si>
-  <si>
-    <t>该关卡累计通关人数。</t>
-  </si>
-  <si>
-    <t>6021</t>
-  </si>
-  <si>
-    <t>该关卡当前最短通关时间，适合作为关卡概览数据。</t>
-  </si>
-  <si>
-    <t>avgClearTime</t>
-  </si>
-  <si>
-    <t>该关卡平均通关时间，可用于评估关卡难度。</t>
   </si>
 </sst>
 </file>
@@ -1613,159 +1576,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="4"/>
-  <cols>
-    <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="60" customWidth="1"/>
-    <col min="5" max="5" width="28" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E7" s="3">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E8" s="3">
-        <v>238</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
 </file>